--- a/ig/ch-vacd/StructureDefinition-ch-vacd-immunization-recommendation.xlsx
+++ b/ig/ch-vacd/StructureDefinition-ch-vacd-immunization-recommendation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$36</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="290">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T10:03:10+00:00</t>
+    <t>2026-06-11T13:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,33 +431,57 @@
     <t>ImmunizationRecommendation.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>ImmunizationRecommendation.extension:indicationCode</t>
+  </si>
+  <si>
+    <t>indicationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-epl-regulated-authorization-limitation-indication-code}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ImmunizationRecommendation.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -465,6 +489,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -599,6 +626,9 @@
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1207,12 +1237,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.05859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="65.05859375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1220,7 +1250,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.0625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.96875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2176,7 +2206,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2195,17 +2225,15 @@
         <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>78</v>
@@ -2242,16 +2270,14 @@
         <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2275,7 +2301,7 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>78</v>
@@ -2286,43 +2312,41 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>78</v>
       </c>
@@ -2370,7 +2394,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2379,7 +2403,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -2399,14 +2423,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2419,22 +2443,26 @@
         <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>78</v>
       </c>
@@ -2482,7 +2510,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2494,27 +2522,27 @@
         <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>152</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2522,10 +2550,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>78</v>
@@ -2537,13 +2565,13 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2594,13 +2622,13 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>78</v>
@@ -2609,10 +2637,10 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>159</v>
@@ -2730,15 +2758,15 @@
         <v>167</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>78</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2746,7 +2774,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>89</v>
@@ -2758,16 +2786,16 @@
         <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2818,10 +2846,10 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>89</v>
@@ -2833,13 +2861,13 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>78</v>
@@ -2847,10 +2875,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2858,11 +2886,11 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G15" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="H15" t="s" s="2">
         <v>78</v>
       </c>
@@ -2870,16 +2898,16 @@
         <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2930,28 +2958,28 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH15" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AH15" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="AI15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>78</v>
@@ -2959,10 +2987,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2970,10 +2998,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -2982,16 +3010,16 @@
         <v>78</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3042,19 +3070,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -3063,7 +3091,7 @@
         <v>78</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>78</v>
@@ -3071,21 +3099,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>78</v>
@@ -3097,17 +3125,15 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3156,19 +3182,19 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -3177,7 +3203,7 @@
         <v>78</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>78</v>
@@ -3185,14 +3211,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3205,26 +3231,24 @@
         <v>78</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
       </c>
@@ -3272,7 +3296,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3293,7 +3317,7 @@
         <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>78</v>
@@ -3301,14 +3325,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3321,22 +3345,26 @@
         <v>78</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
       </c>
@@ -3360,11 +3388,13 @@
         <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>78</v>
@@ -3382,7 +3412,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3394,22 +3424,22 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>203</v>
       </c>
@@ -3422,13 +3452,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>78</v>
@@ -3437,13 +3467,13 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3470,11 +3500,11 @@
         <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -3498,7 +3528,7 @@
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>78</v>
@@ -3507,24 +3537,24 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3532,13 +3562,13 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>78</v>
@@ -3547,13 +3577,13 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3580,37 +3610,35 @@
         <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AA21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>78</v>
@@ -3622,10 +3650,10 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>78</v>
@@ -3633,10 +3661,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3644,28 +3672,28 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3692,37 +3720,37 @@
         <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>113</v>
+        <v>219</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="Z22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="AG22" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>78</v>
@@ -3734,21 +3762,21 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3759,25 +3787,25 @@
         <v>89</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3804,11 +3832,13 @@
         <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>78</v>
@@ -3826,13 +3856,13 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>78</v>
@@ -3844,10 +3874,10 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -3855,10 +3885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3878,16 +3908,16 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3914,13 +3944,11 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -3938,7 +3966,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3953,24 +3981,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3978,13 +4006,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
@@ -3993,13 +4021,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>182</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>183</v>
+        <v>236</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4050,28 +4078,28 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -4079,21 +4107,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4105,17 +4133,15 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -4164,19 +4190,19 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -4185,7 +4211,7 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -4193,14 +4219,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4213,26 +4239,24 @@
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4280,7 +4304,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4301,7 +4325,7 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -4309,42 +4333,46 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4368,13 +4396,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>237</v>
+        <v>78</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -4392,28 +4420,28 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>239</v>
+        <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -4421,10 +4449,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4447,13 +4475,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4480,13 +4508,13 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>78</v>
+        <v>247</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -4504,7 +4532,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>89</v>
@@ -4522,10 +4550,10 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -4533,10 +4561,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4544,7 +4572,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>
@@ -4559,13 +4587,13 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4616,10 +4644,10 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>89</v>
@@ -4634,10 +4662,10 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -4645,10 +4673,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4671,13 +4699,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4728,7 +4756,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4746,10 +4774,10 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -4757,10 +4785,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4780,20 +4808,18 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -4842,7 +4868,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4860,10 +4886,10 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -4871,10 +4897,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4894,19 +4920,19 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4956,7 +4982,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4974,10 +5000,10 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -4985,10 +5011,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4999,7 +5025,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -5011,15 +5037,17 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -5068,13 +5096,13 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>78</v>
@@ -5086,10 +5114,10 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -5097,10 +5125,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5123,13 +5151,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5180,7 +5208,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5195,20 +5223,132 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
       </c>
     </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN35">
+  <autoFilter ref="A1:AN36">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5218,7 +5358,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
+  <conditionalFormatting sqref="A2:AI35">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
